--- a/Run_Backend_Guide.xlsx
+++ b/Run_Backend_Guide.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -719,6 +719,34 @@
       <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Demo — accounts/pulkit/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>vijay</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>4150</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>4154</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Demo — accounts/vijay/ (no crypto account)</t>
         </is>
       </c>
     </row>
@@ -736,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -924,17 +952,43 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>WARNING: before starting any headless bot (storesupportzone.py/store_exit.py/stetergy.py) manually, check it isn't already running — two processes for the same account write to the same files at once (confirmed real bug, hit twice this session). Check with: pgrep -fl "storesupportzone.py|store_exit.py|stetergy.py"</t>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Telegram bot
+(telegrambot.py)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>No (headless)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>cd ~/PycharmProjects/pythonProject/SmartApi
+../venv/bin/python treadingbot/telegrambot.py</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>cd ~/PycharmProjects/pythonProject/SmartApi/accounts/&lt;user&gt;
+../../../venv/bin/python ../../treadingbot/telegrambot.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>WARNING: before starting any headless bot (storesupportzone.py/store_exit.py/stetergy.py/telegrambot.py) manually, check it isn't already running — two processes for the same account write to the same files at once (confirmed real bug, hit twice this session). Check with: pgrep -fl "storesupportzone.py|store_exit.py|stetergy.py|telegrambot.py"
+Note: telegrambot.py only runs for a user once a bot_token is set in their document.py (Admin panel -&gt; that user's Manage -&gt; Telegram section). Currently only chetan has one configured.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -986,7 +1040,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>for pid in $(pgrep -f "storesupportzone.py|store_exit.py|stetergy.py"); do echo "pid=$pid cwd=$(lsof -p \"$pid\" 2&gt;/dev/null | awk '$4==\"cwd\"{print $NF}')"; done</t>
+          <t>for pid in $(pgrep -f "storesupportzone.py|store_exit.py|stetergy.py|telegrambot.py"); do echo "pid=$pid cwd=$(lsof -p \"$pid\" 2&gt;/dev/null | awk '$4==\"cwd\"{print $NF}')"; done</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1003,7 +1057,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>lsof -i :4100,4104,4110,4114,4120,4124,4130,4134,4140,4144,4101,4111,4141</t>
+          <t>lsof -i :4100,4104,4110,4114,4120,4124,4130,4134,4140,4144,4150,4154,4101,4111,4141</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
